--- a/data/Lüterkofen-Ichertswil/investment_decision/Ichertswil_SFH_from_2015_investment_decision.xlsx
+++ b/data/Lüterkofen-Ichertswil/investment_decision/Ichertswil_SFH_from_2015_investment_decision.xlsx
@@ -470,22 +470,22 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
+          <t>scen_cp_cu_invested_available_unit</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>scen_cp_cu_candidate_unit</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
           <t>scen_all_invested_available_unit</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>scen_all_candidate_unit</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>scen_cp_cu_invested_available_unit</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>scen_cp_cu_candidate_unit</t>
         </is>
       </c>
     </row>
@@ -494,7 +494,7 @@
         <v>46023</v>
       </c>
       <c r="B2" t="n">
-        <v>1.156907268488638</v>
+        <v>0.4448614411095393</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -508,19 +508,19 @@
         <v>587.1906533471592</v>
       </c>
       <c r="F2" t="n">
-        <v>1.157723528900741</v>
+        <v>0.4451116081081986</v>
       </c>
       <c r="G2" t="n">
         <v>587.1906533471592</v>
       </c>
       <c r="H2" t="n">
-        <v>1.222213372248918</v>
+        <v>0.3742637930730799</v>
       </c>
       <c r="I2" t="n">
         <v>587.1906533471592</v>
       </c>
       <c r="J2" t="n">
-        <v>1.222213372248918</v>
+        <v>0.3742637930730799</v>
       </c>
       <c r="K2" t="n">
         <v>587.1906533471592</v>
@@ -531,7 +531,7 @@
         <v>47849</v>
       </c>
       <c r="B3" t="n">
-        <v>3.659433668919267</v>
+        <v>2.159515824144617</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -545,19 +545,19 @@
         <v>587.1906533471592</v>
       </c>
       <c r="F3" t="n">
-        <v>3.399001903284045</v>
+        <v>2.162886837942764</v>
       </c>
       <c r="G3" t="n">
         <v>587.1906533471592</v>
       </c>
       <c r="H3" t="n">
-        <v>3.590335380626025</v>
+        <v>2.131288799043</v>
       </c>
       <c r="I3" t="n">
         <v>587.1906533471592</v>
       </c>
       <c r="J3" t="n">
-        <v>3.590335380626025</v>
+        <v>2.162886837942763</v>
       </c>
       <c r="K3" t="n">
         <v>587.1906533471592</v>
@@ -568,7 +568,7 @@
         <v>49675</v>
       </c>
       <c r="B4" t="n">
-        <v>3.659433668919267</v>
+        <v>2.159515824144617</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -582,19 +582,19 @@
         <v>587.1906533471592</v>
       </c>
       <c r="F4" t="n">
-        <v>3.399001903284045</v>
+        <v>2.162886837942764</v>
       </c>
       <c r="G4" t="n">
         <v>587.1906533471592</v>
       </c>
       <c r="H4" t="n">
-        <v>3.590335380626025</v>
+        <v>2.131288799043</v>
       </c>
       <c r="I4" t="n">
         <v>587.1906533471592</v>
       </c>
       <c r="J4" t="n">
-        <v>3.590335380626025</v>
+        <v>2.162886837942763</v>
       </c>
       <c r="K4" t="n">
         <v>587.1906533471592</v>
@@ -605,7 +605,7 @@
         <v>51502</v>
       </c>
       <c r="B5" t="n">
-        <v>3.659433668919267</v>
+        <v>2.159515824144617</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -619,19 +619,19 @@
         <v>587.1906533471592</v>
       </c>
       <c r="F5" t="n">
-        <v>3.399001903284045</v>
+        <v>2.162886837942764</v>
       </c>
       <c r="G5" t="n">
         <v>587.1906533471592</v>
       </c>
       <c r="H5" t="n">
-        <v>3.590335380626025</v>
+        <v>2.131288799043</v>
       </c>
       <c r="I5" t="n">
         <v>587.1906533471592</v>
       </c>
       <c r="J5" t="n">
-        <v>3.590335380626025</v>
+        <v>2.162886837942763</v>
       </c>
       <c r="K5" t="n">
         <v>587.1906533471592</v>
@@ -642,7 +642,7 @@
         <v>53328</v>
       </c>
       <c r="B6" t="n">
-        <v>3.659433668919267</v>
+        <v>4.33980164089021</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -656,19 +656,19 @@
         <v>587.1906533471592</v>
       </c>
       <c r="F6" t="n">
-        <v>3.399001903284045</v>
+        <v>4.339801640890207</v>
       </c>
       <c r="G6" t="n">
         <v>587.1906533471592</v>
       </c>
       <c r="H6" t="n">
-        <v>3.590335380626025</v>
+        <v>4.27818834663244</v>
       </c>
       <c r="I6" t="n">
         <v>587.1906533471592</v>
       </c>
       <c r="J6" t="n">
-        <v>3.602569184765675</v>
+        <v>4.265357386622057</v>
       </c>
       <c r="K6" t="n">
         <v>587.1906533471592</v>
@@ -683,32 +683,32 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>BLVL_VanadiumRedox_s_2 MWh_d_Ichertswil_b_SFH_from_2015</t>
+          <t>BLVL_Li-ion_s_12.5 kWh_d_Ichertswil_b_SFH_from_2015</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>2</v>
+        <v>0.0125</v>
       </c>
       <c r="E7" t="n">
-        <v>0.8807859800207388</v>
+        <v>1.432392808988764</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>0.8807859800207388</v>
+        <v>1.432392808988764</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>0.8807859800207388</v>
+        <v>1.432392808988764</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>0.8807859800207388</v>
+        <v>1.432392808988764</v>
       </c>
     </row>
     <row r="8">
@@ -720,32 +720,32 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>BLVL_VanadiumRedox_s_2 MWh_d_Ichertswil_b_SFH_from_2015</t>
+          <t>BLVL_Li-ion_s_12.5 kWh_d_Ichertswil_b_SFH_from_2015</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>2</v>
+        <v>0.0125</v>
       </c>
       <c r="E8" t="n">
-        <v>0.8807859800207388</v>
+        <v>1.432392808988764</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>0.8807859800207388</v>
+        <v>1.432392808988764</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>0.8807859800207388</v>
+        <v>1.432392808988764</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>0.8807859800207388</v>
+        <v>1.432392808988764</v>
       </c>
     </row>
     <row r="9">
@@ -757,32 +757,32 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>BLVL_VanadiumRedox_s_2 MWh_d_Ichertswil_b_SFH_from_2015</t>
+          <t>BLVL_Li-ion_s_12.5 kWh_d_Ichertswil_b_SFH_from_2015</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>2</v>
+        <v>0.0125</v>
       </c>
       <c r="E9" t="n">
-        <v>0.8807859800207388</v>
+        <v>1.432392808988764</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>0.8807859800207388</v>
+        <v>1.432392808988764</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>0.8807859800207388</v>
+        <v>1.432392808988764</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>0.8807859800207388</v>
+        <v>1.432392808988764</v>
       </c>
     </row>
     <row r="10">
@@ -794,32 +794,32 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>BLVL_VanadiumRedox_s_2 MWh_d_Ichertswil_b_SFH_from_2015</t>
+          <t>BLVL_Li-ion_s_12.5 kWh_d_Ichertswil_b_SFH_from_2015</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>2</v>
+        <v>0.0125</v>
       </c>
       <c r="E10" t="n">
-        <v>0.8807859800207388</v>
+        <v>1.432392808988764</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>0.8807859800207388</v>
+        <v>1.432392808988764</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>0.8807859800207388</v>
+        <v>1.432392808988764</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>0.8807859800207388</v>
+        <v>1.432392808988764</v>
       </c>
     </row>
     <row r="11">
@@ -831,32 +831,32 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>BLVL_VanadiumRedox_s_2 MWh_d_Ichertswil_b_SFH_from_2015</t>
+          <t>BLVL_Li-ion_s_12.5 kWh_d_Ichertswil_b_SFH_from_2015</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>2</v>
+        <v>0.0125</v>
       </c>
       <c r="E11" t="n">
-        <v>0.8807859800207388</v>
+        <v>1.432392808988764</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>0.8807859800207388</v>
+        <v>1.432392808988764</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>0.8807859800207388</v>
+        <v>1.432392808988764</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>0.8807859800207388</v>
+        <v>1.432392808988764</v>
       </c>
     </row>
     <row r="12">
@@ -864,7 +864,7 @@
         <v>46023</v>
       </c>
       <c r="B12" t="n">
-        <v>0.0002822350023529412</v>
+        <v>0.0002208795670588235</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -878,19 +878,19 @@
         <v>1</v>
       </c>
       <c r="F12" t="n">
-        <v>0.0002822350023529412</v>
+        <v>0.0002208795670588235</v>
       </c>
       <c r="G12" t="n">
         <v>1</v>
       </c>
       <c r="H12" t="n">
-        <v>0.0002822350023529412</v>
+        <v>0.00020860848</v>
       </c>
       <c r="I12" t="n">
         <v>1</v>
       </c>
       <c r="J12" t="n">
-        <v>0.0002822350023529412</v>
+        <v>0.00020860848</v>
       </c>
       <c r="K12" t="n">
         <v>1</v>
@@ -901,7 +901,7 @@
         <v>47849</v>
       </c>
       <c r="B13" t="n">
-        <v>0.0002945060894117647</v>
+        <v>0.0002699639152941168</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -915,19 +915,19 @@
         <v>1</v>
       </c>
       <c r="F13" t="n">
-        <v>0.0002945060894117647</v>
+        <v>0.0002699639152941177</v>
       </c>
       <c r="G13" t="n">
         <v>1</v>
       </c>
       <c r="H13" t="n">
-        <v>0.0002945060894117647</v>
+        <v>0.0002576928282352941</v>
       </c>
       <c r="I13" t="n">
         <v>1</v>
       </c>
       <c r="J13" t="n">
-        <v>0.0002945060894117647</v>
+        <v>0.0002699639152941177</v>
       </c>
       <c r="K13" t="n">
         <v>1</v>
@@ -938,7 +938,7 @@
         <v>49675</v>
       </c>
       <c r="B14" t="n">
-        <v>0.0002945060894117647</v>
+        <v>0.0002699639152941177</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -952,19 +952,19 @@
         <v>1</v>
       </c>
       <c r="F14" t="n">
-        <v>0.0002945060894117647</v>
+        <v>0.0002699639152941177</v>
       </c>
       <c r="G14" t="n">
         <v>1</v>
       </c>
       <c r="H14" t="n">
-        <v>0.0002945060894117647</v>
+        <v>0.0002576928282352941</v>
       </c>
       <c r="I14" t="n">
         <v>1</v>
       </c>
       <c r="J14" t="n">
-        <v>0.0002945060894117647</v>
+        <v>0.0002699639152941177</v>
       </c>
       <c r="K14" t="n">
         <v>1</v>
@@ -975,7 +975,7 @@
         <v>51502</v>
       </c>
       <c r="B15" t="n">
-        <v>0.0002945060894117647</v>
+        <v>0.0002699639152941177</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -989,19 +989,19 @@
         <v>1</v>
       </c>
       <c r="F15" t="n">
-        <v>0.0002945060894117647</v>
+        <v>0.0002699639152941177</v>
       </c>
       <c r="G15" t="n">
         <v>1</v>
       </c>
       <c r="H15" t="n">
-        <v>0.0002945060894117647</v>
+        <v>0.0002576928282352941</v>
       </c>
       <c r="I15" t="n">
         <v>1</v>
       </c>
       <c r="J15" t="n">
-        <v>0.0002945060894117647</v>
+        <v>0.0002699639152941177</v>
       </c>
       <c r="K15" t="n">
         <v>1</v>
@@ -1012,7 +1012,7 @@
         <v>53328</v>
       </c>
       <c r="B16" t="n">
-        <v>0.0002945060894117647</v>
+        <v>0.0002699639152941177</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -1026,19 +1026,19 @@
         <v>1</v>
       </c>
       <c r="F16" t="n">
-        <v>0.0002945060894117647</v>
+        <v>0.0002699639152941177</v>
       </c>
       <c r="G16" t="n">
         <v>1</v>
       </c>
       <c r="H16" t="n">
-        <v>0.0002945060894117647</v>
+        <v>0.0002576928282352941</v>
       </c>
       <c r="I16" t="n">
         <v>1</v>
       </c>
       <c r="J16" t="n">
-        <v>0.0002945060894117647</v>
+        <v>0.0002699639152941177</v>
       </c>
       <c r="K16" t="n">
         <v>1</v>
@@ -1049,7 +1049,7 @@
         <v>46023</v>
       </c>
       <c r="B17" t="n">
-        <v>0.09020941379698265</v>
+        <v>0.07391424271801049</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -1063,19 +1063,19 @@
         <v>0.219038904</v>
       </c>
       <c r="F17" t="n">
-        <v>0.09020941379698263</v>
+        <v>0.07400638935309649</v>
       </c>
       <c r="G17" t="n">
         <v>0.219038904</v>
       </c>
       <c r="H17" t="n">
-        <v>0.09020941379698391</v>
+        <v>0.0672047218603124</v>
       </c>
       <c r="I17" t="n">
         <v>0.219038904</v>
       </c>
       <c r="J17" t="n">
-        <v>0.09020941379698391</v>
+        <v>0.0672047218603124</v>
       </c>
       <c r="K17" t="n">
         <v>0.219038904</v>
@@ -1086,7 +1086,7 @@
         <v>47849</v>
       </c>
       <c r="B18" t="n">
-        <v>0.09020941379698265</v>
+        <v>0.07391424271801049</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -1100,19 +1100,19 @@
         <v>0.219038904</v>
       </c>
       <c r="F18" t="n">
-        <v>0.09020941379698265</v>
+        <v>0.07400638935309649</v>
       </c>
       <c r="G18" t="n">
         <v>0.219038904</v>
       </c>
       <c r="H18" t="n">
-        <v>0.09020941379698391</v>
+        <v>0.0672047218603124</v>
       </c>
       <c r="I18" t="n">
         <v>0.219038904</v>
       </c>
       <c r="J18" t="n">
-        <v>0.09020941379698391</v>
+        <v>0.0672047218603124</v>
       </c>
       <c r="K18" t="n">
         <v>0.219038904</v>
@@ -1123,7 +1123,7 @@
         <v>49675</v>
       </c>
       <c r="B19" t="n">
-        <v>0.09020941379698265</v>
+        <v>0.07391424271801049</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -1137,19 +1137,19 @@
         <v>0.219038904</v>
       </c>
       <c r="F19" t="n">
-        <v>0.09020941379698263</v>
+        <v>0.07400638935309649</v>
       </c>
       <c r="G19" t="n">
         <v>0.219038904</v>
       </c>
       <c r="H19" t="n">
-        <v>0.09020941379698391</v>
+        <v>0.0672047218603124</v>
       </c>
       <c r="I19" t="n">
         <v>0.219038904</v>
       </c>
       <c r="J19" t="n">
-        <v>0.09020941379698391</v>
+        <v>0.0672047218603124</v>
       </c>
       <c r="K19" t="n">
         <v>0.219038904</v>
@@ -1160,7 +1160,7 @@
         <v>51502</v>
       </c>
       <c r="B20" t="n">
-        <v>0.07730109310451846</v>
+        <v>0.0725431088814258</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -1174,19 +1174,19 @@
         <v>0.219038904</v>
       </c>
       <c r="F20" t="n">
-        <v>0.07730109310451848</v>
+        <v>0.07266471802846658</v>
       </c>
       <c r="G20" t="n">
         <v>0.219038904</v>
       </c>
       <c r="H20" t="n">
-        <v>0.07730109310451846</v>
+        <v>0.03087696197833076</v>
       </c>
       <c r="I20" t="n">
         <v>0.219038904</v>
       </c>
       <c r="J20" t="n">
-        <v>0.07730109310451846</v>
+        <v>0.03123348357962814</v>
       </c>
       <c r="K20" t="n">
         <v>0.219038904</v>
@@ -1197,7 +1197,7 @@
         <v>53328</v>
       </c>
       <c r="B21" t="n">
-        <v>0.07730109310451846</v>
+        <v>0.0725431088814258</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -1211,19 +1211,19 @@
         <v>0.219038904</v>
       </c>
       <c r="F21" t="n">
-        <v>0.07730109310451848</v>
+        <v>0.07266471802846658</v>
       </c>
       <c r="G21" t="n">
         <v>0.219038904</v>
       </c>
       <c r="H21" t="n">
-        <v>0.07730109310451846</v>
+        <v>0.03087696197833076</v>
       </c>
       <c r="I21" t="n">
         <v>0.219038904</v>
       </c>
       <c r="J21" t="n">
-        <v>0.07730109310451846</v>
+        <v>0.03123348357962814</v>
       </c>
       <c r="K21" t="n">
         <v>0.219038904</v>
@@ -1419,7 +1419,7 @@
         <v>46023</v>
       </c>
       <c r="B27" t="n">
-        <v>0</v>
+        <v>0.02605944390769238</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -1433,19 +1433,19 @@
         <v>0.219038904</v>
       </c>
       <c r="F27" t="n">
-        <v>0</v>
+        <v>0.02595749930109333</v>
       </c>
       <c r="G27" t="n">
         <v>0.219038904</v>
       </c>
       <c r="H27" t="n">
-        <v>0</v>
+        <v>0.03553397273230079</v>
       </c>
       <c r="I27" t="n">
         <v>0.219038904</v>
       </c>
       <c r="J27" t="n">
-        <v>0</v>
+        <v>0.03553397273230079</v>
       </c>
       <c r="K27" t="n">
         <v>0.219038904</v>
@@ -1456,7 +1456,7 @@
         <v>47849</v>
       </c>
       <c r="B28" t="n">
-        <v>0</v>
+        <v>0.02605944390769238</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -1470,19 +1470,19 @@
         <v>0.219038904</v>
       </c>
       <c r="F28" t="n">
-        <v>0</v>
+        <v>0.02595749930109333</v>
       </c>
       <c r="G28" t="n">
         <v>0.219038904</v>
       </c>
       <c r="H28" t="n">
-        <v>0</v>
+        <v>0.04541320664973464</v>
       </c>
       <c r="I28" t="n">
         <v>0.219038904</v>
       </c>
       <c r="J28" t="n">
-        <v>0</v>
+        <v>0.04563310500000001</v>
       </c>
       <c r="K28" t="n">
         <v>0.219038904</v>
@@ -1493,7 +1493,7 @@
         <v>49675</v>
       </c>
       <c r="B29" t="n">
-        <v>0</v>
+        <v>0.02605944390769237</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -1507,19 +1507,19 @@
         <v>0.219038904</v>
       </c>
       <c r="F29" t="n">
-        <v>0</v>
+        <v>0.02595749930109333</v>
       </c>
       <c r="G29" t="n">
         <v>0.219038904</v>
       </c>
       <c r="H29" t="n">
-        <v>0</v>
+        <v>0.04840625070753644</v>
       </c>
       <c r="I29" t="n">
         <v>0.219038904</v>
       </c>
       <c r="J29" t="n">
-        <v>0</v>
+        <v>0.04897245187269918</v>
       </c>
       <c r="K29" t="n">
         <v>0.219038904</v>
@@ -1530,7 +1530,7 @@
         <v>51502</v>
       </c>
       <c r="B30" t="n">
-        <v>0</v>
+        <v>0.006231518784608491</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -1544,19 +1544,19 @@
         <v>0.219038904</v>
       </c>
       <c r="F30" t="n">
-        <v>0</v>
+        <v>0.006109909637567705</v>
       </c>
       <c r="G30" t="n">
         <v>0.219038904</v>
       </c>
       <c r="H30" t="n">
-        <v>0</v>
+        <v>0.04789766568770353</v>
       </c>
       <c r="I30" t="n">
         <v>0.219038904</v>
       </c>
       <c r="J30" t="n">
-        <v>0</v>
+        <v>0.04754114408640614</v>
       </c>
       <c r="K30" t="n">
         <v>0.219038904</v>
@@ -1567,7 +1567,7 @@
         <v>53328</v>
       </c>
       <c r="B31" t="n">
-        <v>0</v>
+        <v>0.006231518784608491</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -1581,19 +1581,19 @@
         <v>0.219038904</v>
       </c>
       <c r="F31" t="n">
-        <v>0</v>
+        <v>0.006109909637567705</v>
       </c>
       <c r="G31" t="n">
         <v>0.219038904</v>
       </c>
       <c r="H31" t="n">
-        <v>0</v>
+        <v>0.03801843177026968</v>
       </c>
       <c r="I31" t="n">
         <v>0.219038904</v>
       </c>
       <c r="J31" t="n">
-        <v>0</v>
+        <v>0.03744201181870692</v>
       </c>
       <c r="K31" t="n">
         <v>0.219038904</v>
@@ -2381,7 +2381,7 @@
         <v>47849</v>
       </c>
       <c r="B53" t="n">
-        <v>0.2712660023076275</v>
+        <v>0.2666650335788849</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -2395,19 +2395,19 @@
         <v>0.8766252603832793</v>
       </c>
       <c r="F53" t="n">
-        <v>0.1945850077349957</v>
+        <v>0.1747094073424137</v>
       </c>
       <c r="G53" t="n">
         <v>0.8766252603832793</v>
       </c>
       <c r="H53" t="n">
-        <v>0.1661633658668592</v>
+        <v>0.2633747001357786</v>
       </c>
       <c r="I53" t="n">
         <v>0.8766252603832793</v>
       </c>
       <c r="J53" t="n">
-        <v>0.2697417753599825</v>
+        <v>0.1668555719724274</v>
       </c>
       <c r="K53" t="n">
         <v>0.8766252603832793</v>
@@ -2418,7 +2418,7 @@
         <v>49675</v>
       </c>
       <c r="B54" t="n">
-        <v>0.2712660023076275</v>
+        <v>0.2666650335788849</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -2432,19 +2432,19 @@
         <v>0.8766252603832793</v>
       </c>
       <c r="F54" t="n">
-        <v>0.1945850077349957</v>
+        <v>0.1747094073424137</v>
       </c>
       <c r="G54" t="n">
         <v>0.8766252603832793</v>
       </c>
       <c r="H54" t="n">
-        <v>0.1661633658668592</v>
+        <v>0.2633747001357786</v>
       </c>
       <c r="I54" t="n">
         <v>0.8766252603832793</v>
       </c>
       <c r="J54" t="n">
-        <v>0.2697417753599825</v>
+        <v>0.1668555719724273</v>
       </c>
       <c r="K54" t="n">
         <v>0.8766252603832793</v>
@@ -2455,7 +2455,7 @@
         <v>51502</v>
       </c>
       <c r="B55" t="n">
-        <v>0.2712660023076275</v>
+        <v>0.2666650335788849</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -2469,19 +2469,19 @@
         <v>0.8766252603832793</v>
       </c>
       <c r="F55" t="n">
-        <v>0.1945850077349957</v>
+        <v>0.1747094073424137</v>
       </c>
       <c r="G55" t="n">
         <v>0.8766252603832793</v>
       </c>
       <c r="H55" t="n">
-        <v>0.1661633658668592</v>
+        <v>0.2633747001357786</v>
       </c>
       <c r="I55" t="n">
         <v>0.8766252603832793</v>
       </c>
       <c r="J55" t="n">
-        <v>0.2697417753599825</v>
+        <v>0.1668555719724273</v>
       </c>
       <c r="K55" t="n">
         <v>0.8766252603832793</v>
@@ -2492,7 +2492,7 @@
         <v>53328</v>
       </c>
       <c r="B56" t="n">
-        <v>0.2706722469485929</v>
+        <v>0.2761035250997737</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -2506,19 +2506,19 @@
         <v>0.8766252603832793</v>
       </c>
       <c r="F56" t="n">
-        <v>0.2487754850203192</v>
+        <v>0.2681561652288508</v>
       </c>
       <c r="G56" t="n">
         <v>0.8766252603832793</v>
       </c>
       <c r="H56" t="n">
-        <v>0.2364756104166607</v>
+        <v>0.2695114274051356</v>
       </c>
       <c r="I56" t="n">
         <v>0.8766252603832793</v>
       </c>
       <c r="J56" t="n">
-        <v>0.2690799389636799</v>
+        <v>0.2624806605629156</v>
       </c>
       <c r="K56" t="n">
         <v>0.8766252603832793</v>
@@ -2751,7 +2751,7 @@
         <v>47849</v>
       </c>
       <c r="B63" t="n">
-        <v>0.1831522157519862</v>
+        <v>0.09352433350998071</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -2765,19 +2765,19 @@
         <v>0.8766252603832793</v>
       </c>
       <c r="F63" t="n">
-        <v>0.1946418524711872</v>
+        <v>0.09670069561222769</v>
       </c>
       <c r="G63" t="n">
         <v>0.8766252603832793</v>
       </c>
       <c r="H63" t="n">
-        <v>0.1892684414119822</v>
+        <v>0.09385584576352225</v>
       </c>
       <c r="I63" t="n">
         <v>0.8766252603832793</v>
       </c>
       <c r="J63" t="n">
-        <v>0.184725659098604</v>
+        <v>0.09670069561222765</v>
       </c>
       <c r="K63" t="n">
         <v>0.8766252603832793</v>
@@ -2788,7 +2788,7 @@
         <v>49675</v>
       </c>
       <c r="B64" t="n">
-        <v>0.1831522157519862</v>
+        <v>0.09352433350998071</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -2802,19 +2802,19 @@
         <v>0.8766252603832793</v>
       </c>
       <c r="F64" t="n">
-        <v>0.1946418524711872</v>
+        <v>0.09670069561222769</v>
       </c>
       <c r="G64" t="n">
         <v>0.8766252603832793</v>
       </c>
       <c r="H64" t="n">
-        <v>0.1892684414119822</v>
+        <v>0.09385584576352225</v>
       </c>
       <c r="I64" t="n">
         <v>0.8766252603832793</v>
       </c>
       <c r="J64" t="n">
-        <v>0.184725659098604</v>
+        <v>0.09670069561222765</v>
       </c>
       <c r="K64" t="n">
         <v>0.8766252603832793</v>
@@ -2825,7 +2825,7 @@
         <v>51502</v>
       </c>
       <c r="B65" t="n">
-        <v>0.1831522157519862</v>
+        <v>0.09352433350998071</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -2839,19 +2839,19 @@
         <v>0.8766252603832793</v>
       </c>
       <c r="F65" t="n">
-        <v>0.1946418524711872</v>
+        <v>0.09670069561222769</v>
       </c>
       <c r="G65" t="n">
         <v>0.8766252603832793</v>
       </c>
       <c r="H65" t="n">
-        <v>0.1892684414119822</v>
+        <v>0.09385584576352225</v>
       </c>
       <c r="I65" t="n">
         <v>0.8766252603832793</v>
       </c>
       <c r="J65" t="n">
-        <v>0.184725659098604</v>
+        <v>0.09670069561222765</v>
       </c>
       <c r="K65" t="n">
         <v>0.8766252603832793</v>
@@ -2862,7 +2862,7 @@
         <v>53328</v>
       </c>
       <c r="B66" t="n">
-        <v>0.2149107063495496</v>
+        <v>0.06718855571430085</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -2876,19 +2876,19 @@
         <v>0.8766252603832793</v>
       </c>
       <c r="F66" t="n">
-        <v>0.2425522866374238</v>
+        <v>0.07513591558522385</v>
       </c>
       <c r="G66" t="n">
         <v>0.8766252603832793</v>
       </c>
       <c r="H66" t="n">
-        <v>0.2506315698291268</v>
+        <v>0.07608770001174633</v>
       </c>
       <c r="I66" t="n">
         <v>0.8766252603832793</v>
       </c>
       <c r="J66" t="n">
-        <v>0.2177573779554977</v>
+        <v>0.08257320628417504</v>
       </c>
       <c r="K66" t="n">
         <v>0.8766252603832793</v>
@@ -3306,7 +3306,7 @@
         <v>47849</v>
       </c>
       <c r="B78" t="n">
-        <v>0</v>
+        <v>0.003585146609091578</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -3320,19 +3320,19 @@
         <v>0.8766252603832793</v>
       </c>
       <c r="F78" t="n">
-        <v>0.07093617621303135</v>
+        <v>0.0923327421596187</v>
       </c>
       <c r="G78" t="n">
         <v>0.8766252603832793</v>
       </c>
       <c r="H78" t="n">
-        <v>0.1005106377284174</v>
+        <v>0.007587643495443875</v>
       </c>
       <c r="I78" t="n">
         <v>0.8766252603832793</v>
       </c>
       <c r="J78" t="n">
-        <v>0.001475010548672281</v>
+        <v>0.1001865775296051</v>
       </c>
       <c r="K78" t="n">
         <v>0.8766252603832793</v>
@@ -3343,7 +3343,7 @@
         <v>49675</v>
       </c>
       <c r="B79" t="n">
-        <v>0</v>
+        <v>0.003585146609091578</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -3357,19 +3357,19 @@
         <v>0.8766252603832793</v>
       </c>
       <c r="F79" t="n">
-        <v>0.07093617621303135</v>
+        <v>0.0923327421596187</v>
       </c>
       <c r="G79" t="n">
         <v>0.8766252603832793</v>
       </c>
       <c r="H79" t="n">
-        <v>0.1005106377284174</v>
+        <v>0.007587643495443875</v>
       </c>
       <c r="I79" t="n">
         <v>0.8766252603832793</v>
       </c>
       <c r="J79" t="n">
-        <v>0.001475010548672281</v>
+        <v>0.1001865775296051</v>
       </c>
       <c r="K79" t="n">
         <v>0.8766252603832793</v>
@@ -3380,7 +3380,7 @@
         <v>51502</v>
       </c>
       <c r="B80" t="n">
-        <v>0</v>
+        <v>0.003585146609091578</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -3394,19 +3394,19 @@
         <v>0.8766252603832793</v>
       </c>
       <c r="F80" t="n">
-        <v>0.07093617621303135</v>
+        <v>0.0923327421596187</v>
       </c>
       <c r="G80" t="n">
         <v>0.8766252603832793</v>
       </c>
       <c r="H80" t="n">
-        <v>0.1005106377284174</v>
+        <v>0.007587643495443875</v>
       </c>
       <c r="I80" t="n">
         <v>0.8766252603832793</v>
       </c>
       <c r="J80" t="n">
-        <v>0.001475010548672281</v>
+        <v>0.1001865775296051</v>
       </c>
       <c r="K80" t="n">
         <v>0.8766252603832793</v>
